--- a/data/trans_camb/P1429-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1429-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,75</t>
+          <t>-2,63; -0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,4</t>
+          <t>-2,47; -0,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,46</t>
+          <t>-1,05; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,82</t>
+          <t>-1,46; 2,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,41</t>
+          <t>-3,03; 1,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,99</t>
+          <t>1,75; 5,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,9</t>
+          <t>-1,64; 0,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,16</t>
+          <t>-2,38; 0,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,88</t>
+          <t>1,09; 3,94</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,53</t>
+          <t>-100,0; 6,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-90,9; -17,39</t>
+          <t>-90,52; -10,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 101,33</t>
+          <t>-44,2; 104,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 43,05</t>
+          <t>-17,18; 43,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 21,0</t>
+          <t>-36,51; 23,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 91,24</t>
+          <t>19,4; 90,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 18,78</t>
+          <t>-29,31; 20,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 3,71</t>
+          <t>-40,81; 9,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,6; 84,75</t>
+          <t>18,49; 88,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; -0,07</t>
+          <t>-0,88; -0,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,04</t>
+          <t>-0,83; 0,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,69</t>
+          <t>-0,4; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,04</t>
+          <t>-1,94; 0,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,88</t>
+          <t>-1,19; 0,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,05</t>
+          <t>-0,57; 1,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,24</t>
+          <t>-1,21; -0,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,3</t>
+          <t>-0,8; 0,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,75</t>
+          <t>-0,28; 0,83</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-95,43; 9,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-89,22; 40,22</t>
+          <t>-89,44; 42,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 224,01</t>
+          <t>-54,25; 229,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,27; -1,45</t>
+          <t>-64,35; 4,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 50,99</t>
+          <t>-40,49; 45,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 55,8</t>
+          <t>-18,52; 80,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,53; -17,32</t>
+          <t>-68,17; -15,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 27,22</t>
+          <t>-45,9; 25,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 68,13</t>
+          <t>-16,55; 72,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,15</t>
+          <t>-1,67; -0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,58</t>
+          <t>-1,14; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,38</t>
+          <t>-1,39; 0,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,32</t>
+          <t>-1,02; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,1</t>
+          <t>-1,04; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,43</t>
+          <t>-0,06; 2,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,86</t>
+          <t>-0,88; 0,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,27</t>
+          <t>-0,73; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,26</t>
+          <t>-0,35; 1,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-36,44%</t>
+          <t>-39,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 369,67</t>
+          <t>-59,98; 327,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 336,21</t>
+          <t>-58,29; 307,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 382,71</t>
+          <t>-14,27; 428,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 168,09</t>
+          <t>-68,92; 183,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 266,57</t>
+          <t>-56,17; 195,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 226,74</t>
+          <t>-26,32; 233,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,51</t>
+          <t>-1,24; -0,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; -0,3</t>
+          <t>-1,11; -0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,29</t>
+          <t>-0,68; 0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,7</t>
+          <t>-1,24; 0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,11</t>
+          <t>-1,67; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,99</t>
+          <t>-0,48; 1,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,06</t>
+          <t>-1,1; -0,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,27</t>
+          <t>-1,24; -0,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,49</t>
+          <t>-0,36; 0,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-20,38%</t>
+          <t>-18,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,69%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-94,52; -51,71</t>
+          <t>-94,38; -53,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,27; -36,85</t>
+          <t>-83,95; -38,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 39,03</t>
+          <t>-52,12; 36,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 18,66</t>
+          <t>-26,14; 20,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 3,09</t>
+          <t>-35,71; 8,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 26,45</t>
+          <t>-9,96; 36,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,85; -1,77</t>
+          <t>-36,66; 0,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -10,81</t>
+          <t>-42,26; -10,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 20,73</t>
+          <t>-12,2; 25,77</t>
         </is>
       </c>
     </row>
